--- a/data/ReporteHS.xlsx
+++ b/data/ReporteHS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki.costa\Downloads\GitHub_Repositories\Sistema-Pago-Horas-Extras\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8137069-8810-4165-BC99-907E671B6ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31031CEC-0201-4C60-961F-7E2DA56B285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4BE4AC7-3F66-48BA-9752-288A1F5CE175}"/>
+    <workbookView xWindow="6615" yWindow="2250" windowWidth="23745" windowHeight="12480" xr2:uid="{C4BE4AC7-3F66-48BA-9752-288A1F5CE175}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>WHATSAPP</t>
   </si>
@@ -68,41 +68,22 @@
     <t>ESTADO</t>
   </si>
   <si>
-    <t>whatsapp:+5491128760418</t>
-  </si>
-  <si>
-    <t>Dante Herrera</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>29/11/2025</t>
-  </si>
-  <si>
-    <t>07:52</t>
-  </si>
-  <si>
-    <t>18:04</t>
-  </si>
-  <si>
-    <t>Sin información aún</t>
-  </si>
-  <si>
-    <t>SIN INFORMACIÓN</t>
-  </si>
-  <si>
-    <t>Fernandez</t>
+    <t>Milagros</t>
+  </si>
+  <si>
+    <t>Vanesa</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+  <numFmts count="2">
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
-    <numFmt numFmtId="168" formatCode="[h]:mm:ss;@"/>
+    <numFmt numFmtId="166" formatCode="[h]:mm:ss;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -177,16 +158,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -199,7 +176,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -536,21 +513,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B577673B-7B1E-48CB-ACAB-7FDE97BCB816}">
-  <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,119 +559,86 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="D2" s="6">
+        <v>46111</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46111</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H2" s="7">
+        <f t="shared" ref="H2:H3" si="0">IF(G2&lt;F2, G2+1-F2, G2-F2)</f>
+        <v>0.5</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="6">
+        <v>46112</v>
+      </c>
+      <c r="E3" s="6">
+        <v>46112</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H3" s="7">
+        <f t="shared" si="0"/>
+        <v>0.37500000000000006</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="9">
-        <f>IF(G2&lt;F2, G2+1-F2, G2-F2)</f>
-        <v>0.42499999999999999</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="6"/>
-      <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="C4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6">
+        <v>46114</v>
+      </c>
+      <c r="E4" s="6">
+        <v>46114</v>
+      </c>
+      <c r="F4" s="5">
         <v>0.33333333333333331</v>
       </c>
-      <c r="G3" s="7">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="H3" s="9">
-        <f t="shared" ref="H3:H5" si="0">IF(G3&lt;F3, G3+1-F3, G3-F3)</f>
-        <v>0.5</v>
-      </c>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="8">
-        <v>45991</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0.20833333333333334</v>
-      </c>
-      <c r="H4" s="9">
-        <f t="shared" si="0"/>
-        <v>0.875</v>
-      </c>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="8">
-        <v>45991</v>
-      </c>
-      <c r="F5" s="7">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="G5" s="7">
-        <v>0.29166666666666669</v>
-      </c>
-      <c r="H5" s="9">
-        <f>IF(G5&lt;F5, G5+1-F5, G5-F5)</f>
-        <v>0.95833333333333348</v>
-      </c>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
+      <c r="G4" s="5">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4" si="1">IF(G4&lt;F4, G4+1-F4, G4-F4)</f>
+        <v>0.64583333333333326</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/ReporteHS.xlsx
+++ b/data/ReporteHS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\inaki.costa\Downloads\GitHub_Repositories\Sistema-Pago-Horas-Extras\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31031CEC-0201-4C60-961F-7E2DA56B285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA0E20B4-3D84-41C8-BAE6-DA9049BB9D75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6615" yWindow="2250" windowWidth="23745" windowHeight="12480" xr2:uid="{C4BE4AC7-3F66-48BA-9752-288A1F5CE175}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C4BE4AC7-3F66-48BA-9752-288A1F5CE175}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
   <si>
     <t>WHATSAPP</t>
   </si>
@@ -71,10 +71,10 @@
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>Milagros</t>
-  </si>
-  <si>
-    <t>Vanesa</t>
+    <t>AYLEN SANCHEZ</t>
+  </si>
+  <si>
+    <t>JULIA FERNANDEZ</t>
   </si>
 </sst>
 </file>
@@ -82,8 +82,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="165" formatCode="h:mm;@"/>
-    <numFmt numFmtId="166" formatCode="[h]:mm:ss;@"/>
+    <numFmt numFmtId="164" formatCode="h:mm;@"/>
+    <numFmt numFmtId="165" formatCode="[h]:mm:ss;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -170,13 +170,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Neutral" xfId="1" builtinId="28"/>
@@ -513,21 +513,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B577673B-7B1E-48CB-ACAB-7FDE97BCB816}">
-  <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -559,9 +559,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="4"/>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -586,19 +586,19 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="4"/>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="6">
-        <v>46112</v>
+        <v>46146</v>
       </c>
       <c r="E3" s="6">
-        <v>46112</v>
+        <v>46146</v>
       </c>
       <c r="F3" s="5">
         <v>0.33333333333333331</v>
@@ -613,32 +613,173 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="6">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="E4" s="6">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="F4" s="5">
         <v>0.33333333333333331</v>
       </c>
       <c r="G4" s="5">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4:H10" si="1">IF(G4&lt;F4, G4+1-F4, G4-F4)</f>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="6">
+        <v>46114</v>
+      </c>
+      <c r="E5" s="6">
+        <v>46114</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G5" s="5">
         <v>0.97916666666666663</v>
       </c>
-      <c r="H4" s="7">
-        <f t="shared" ref="H4" si="1">IF(G4&lt;F4, G4+1-F4, G4-F4)</f>
-        <v>0.64583333333333326</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="H5" s="7">
+        <f t="shared" si="1"/>
+        <v>0.5625</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6">
+        <v>46115</v>
+      </c>
+      <c r="E6" s="6">
+        <v>46115</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="6">
+        <v>46147</v>
+      </c>
+      <c r="E7" s="6">
+        <v>46148</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.25</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333337</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="6">
+        <v>46148</v>
+      </c>
+      <c r="E8" s="6">
+        <v>46148</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="1"/>
+        <v>0.39583333333333337</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D9" s="6">
+        <v>46149</v>
+      </c>
+      <c r="E9" s="6">
+        <v>46149</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.27083333333333331</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="1"/>
+        <v>0.43750000000000006</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" s="6">
+        <v>46150</v>
+      </c>
+      <c r="E10" s="6">
+        <v>46150</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.375</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333337</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
